--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/los-lagos.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/los-lagos.xlsx
@@ -623,7 +623,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1387,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1574,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1639,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1704,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1769,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1834,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2021,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2147,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2395,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2460,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2586,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2651,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2716,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3025,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3395,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3586,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3651,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3716,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3781,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3846,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3911,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4098,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4285,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4411,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4537,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4602,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4789,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4915,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4980,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5228,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5415,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5541,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5606,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5671,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5736,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5801,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5866,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5931,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6118,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6183,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6248,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6313,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6378,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6443,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6569,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6634,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6699,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6947,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7012,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7077,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7329,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7394,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7581,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7707,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8016,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8268,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8333,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8398,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8524,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8589,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8776,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8902,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9089,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9154,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9402,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9467,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9532,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9597,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9784,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9971,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10036,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10101,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10227,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10292,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10418,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10605,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10670,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10735,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10800,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10926,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10991,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11117,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11182,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11308,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11434,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11804,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12296,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12483,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12548,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12735,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12800,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12865,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12991,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13056,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13121,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13247,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13312,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13621,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13747,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13934,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14121,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14186,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14251,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14377,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14442,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14568,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14633,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14759,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14824,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14889,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15015,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15080,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15389,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15454,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15519,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15889,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16076,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16141,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16206,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16271,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16397,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16523,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16649,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17019,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17084,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17149,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17214,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17279,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17466,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17714,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +17962,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18149,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18275,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18584,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +18832,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +18897,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19023,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19271,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19336,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19523,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19710,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +19775,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19901,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +19966,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20397,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20462,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20588,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20653,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20840,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +20966,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21153,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21279,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21344,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21409,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21535,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21600,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21726,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +21913,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +21978,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22226,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22474,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +22722,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22787,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +22913,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +22978,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23043,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23108,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23234,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23482,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23547,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23612,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24104,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +24657,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +24783,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +24848,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +24913,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +24978,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25287,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +25535,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +25661,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +25787,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +25852,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +25917,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26409,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26474,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +26661,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +26909,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +26974,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +27161,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27287,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27413,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +27478,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +27604,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +27669,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +27734,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +27799,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +27864,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +27929,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +27994,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28059,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28124,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28250,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28315,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +28441,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +28506,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +28693,11 @@
           <t>77.714.552-5</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +28758,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +28823,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +28949,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28260,7 +29140,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28321,7 +29205,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28565,7 +29453,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28748,7 +29640,11 @@
           <t>77.630.237-6</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28809,7 +29705,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29053,7 +29953,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29175,7 +30079,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29297,7 +30205,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29358,7 +30270,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29419,7 +30335,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29480,7 +30400,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +30465,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +30530,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29663,7 +30595,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29724,7 +30660,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29785,7 +30725,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +30973,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +31099,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +31164,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30273,7 +31229,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30395,7 +31355,11 @@
           <t>77.916.035-1</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +31420,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30517,7 +31485,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +31611,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +31676,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30883,7 +31863,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31005,7 +31989,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +32054,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +32119,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +32184,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31249,7 +32249,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31432,7 +32436,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31493,7 +32501,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +32566,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +32631,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31676,7 +32696,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31859,7 +32883,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31920,7 +32948,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +33013,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32042,7 +33078,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +33143,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32290,7 +33334,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32351,7 +33399,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32412,7 +33464,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32473,7 +33529,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32534,7 +33594,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32839,7 +33903,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32961,7 +34029,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33083,7 +34155,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33205,7 +34281,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33449,7 +34529,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33510,7 +34594,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33571,7 +34659,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33693,7 +34785,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33876,7 +34972,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33937,7 +35037,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33998,7 +35102,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34059,7 +35167,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34242,7 +35354,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34364,7 +35480,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34425,7 +35545,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34486,7 +35610,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34547,7 +35675,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34669,7 +35801,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34730,7 +35866,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34791,7 +35931,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34852,7 +35996,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34913,7 +36061,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35035,7 +36187,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35096,7 +36252,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35157,7 +36317,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35279,7 +36443,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35340,7 +36508,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35462,7 +36634,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35523,7 +36699,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35584,7 +36764,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35645,7 +36829,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35767,7 +36955,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35828,7 +37020,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35889,7 +37085,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35950,7 +37150,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36011,7 +37215,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36072,7 +37280,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36255,7 +37467,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36377,7 +37593,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36438,7 +37658,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36499,7 +37723,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37109,7 +38337,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37170,7 +38402,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37231,7 +38467,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37292,7 +38532,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37414,7 +38658,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37536,7 +38784,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37597,7 +38849,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37719,7 +38975,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37902,7 +39162,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37963,7 +39227,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38146,7 +39414,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38268,7 +39540,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38329,7 +39605,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38390,7 +39670,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38451,7 +39735,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38512,7 +39800,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38573,7 +39865,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38634,7 +39930,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38756,7 +40056,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38939,7 +40243,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39000,7 +40308,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39061,7 +40373,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39122,7 +40438,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39183,7 +40503,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39305,7 +40629,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39427,7 +40755,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39488,7 +40820,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39549,7 +40885,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39610,7 +40950,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39671,7 +41015,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39854,7 +41202,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39915,7 +41267,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40037,7 +41393,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40220,7 +41580,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40281,7 +41645,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40342,7 +41710,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40464,7 +41836,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40525,7 +41901,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40586,7 +41966,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40708,7 +42092,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40830,7 +42218,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40952,7 +42344,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41013,7 +42409,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41135,7 +42535,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41196,7 +42600,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41379,7 +42787,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41440,7 +42852,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41501,7 +42917,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41623,7 +43043,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41684,7 +43108,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41745,7 +43173,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41867,7 +43299,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41928,7 +43364,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41989,7 +43429,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42050,7 +43494,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42172,7 +43620,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42294,7 +43746,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42355,7 +43811,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42477,7 +43937,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42538,7 +44002,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42599,7 +44067,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42660,7 +44132,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42721,7 +44197,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42904,7 +44384,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42965,7 +44449,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43026,7 +44514,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43087,7 +44579,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43148,7 +44644,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43209,7 +44709,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43270,7 +44774,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43331,7 +44839,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43392,7 +44904,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43514,7 +45030,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43880,7 +45400,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44124,7 +45648,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44551,7 +46079,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44673,7 +46205,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44734,7 +46270,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44917,7 +46457,11 @@
           <t>77.916.035-1</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44978,7 +46522,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45100,7 +46648,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45161,7 +46713,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45222,7 +46778,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45405,7 +46965,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45466,7 +47030,11 @@
           <t>77.916.035-1</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45588,7 +47156,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45893,7 +47465,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45954,7 +47530,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46198,7 +47778,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46259,7 +47843,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46381,7 +47969,11 @@
           <t>78.007.139-7</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46625,7 +48217,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46808,7 +48404,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46869,7 +48469,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46930,7 +48534,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L762" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46991,7 +48599,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47113,7 +48725,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47235,7 +48851,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47357,7 +48977,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47479,7 +49103,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47540,7 +49168,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L772" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47784,7 +49416,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L776" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47845,7 +49481,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K777" t="inlineStr"/>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L777" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47967,7 +49607,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48150,7 +49794,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L782" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48211,7 +49859,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K783" t="inlineStr"/>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L783" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48638,7 +50290,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48699,7 +50355,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48760,7 +50420,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L792" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48821,7 +50485,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L793" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49004,7 +50672,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L796" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49065,7 +50737,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K797" t="inlineStr"/>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L797" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49126,7 +50802,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L798" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49309,7 +50989,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49370,7 +51054,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L802" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49431,7 +51119,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K803" t="inlineStr"/>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L803" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49492,7 +51184,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L804" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49553,7 +51249,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L805" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49614,7 +51314,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49736,7 +51440,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K808" t="inlineStr"/>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L808" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50041,7 +51749,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K813" t="inlineStr"/>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L813" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50163,7 +51875,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K815" t="inlineStr"/>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L815" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50224,7 +51940,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K816" t="inlineStr"/>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L816" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50285,7 +52005,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K817" t="inlineStr"/>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L817" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50346,7 +52070,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K818" t="inlineStr"/>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L818" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50407,7 +52135,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K819" t="inlineStr"/>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L819" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50529,7 +52261,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K821" t="inlineStr"/>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L821" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50712,7 +52448,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K824" t="inlineStr"/>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L824" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50773,7 +52513,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L825" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50834,7 +52578,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K826" t="inlineStr"/>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L826" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50895,7 +52643,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K827" t="inlineStr"/>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L827" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51017,7 +52769,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K829" t="inlineStr"/>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L829" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51139,7 +52895,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K831" t="inlineStr"/>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L831" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51322,7 +53082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K834" t="inlineStr"/>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L834" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51383,7 +53147,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L835" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51444,7 +53212,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K836" t="inlineStr"/>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L836" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51505,7 +53277,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K837" t="inlineStr"/>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L837" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51566,7 +53342,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L838" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51932,7 +53712,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K844" t="inlineStr"/>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L844" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51993,7 +53777,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K845" t="inlineStr"/>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L845" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52054,7 +53842,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K846" t="inlineStr"/>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L846" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52115,7 +53907,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K847" t="inlineStr"/>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L847" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52298,7 +54094,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K850" t="inlineStr"/>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L850" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52420,7 +54220,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K852" t="inlineStr"/>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L852" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52603,7 +54407,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K855" t="inlineStr"/>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L855" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52664,7 +54472,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K856" t="inlineStr"/>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L856" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52786,7 +54598,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K858" t="inlineStr"/>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L858" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52969,7 +54785,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K861" t="inlineStr"/>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L861" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53091,7 +54911,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K863" t="inlineStr"/>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L863" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53457,7 +55281,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K869" t="inlineStr"/>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L869" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53579,7 +55407,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K871" t="inlineStr"/>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L871" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53640,7 +55472,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K872" t="inlineStr"/>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L872" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53701,7 +55537,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K873" t="inlineStr"/>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L873" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53762,7 +55602,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K874" t="inlineStr"/>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L874" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53884,7 +55728,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K876" t="inlineStr"/>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L876" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54006,7 +55854,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K878" t="inlineStr"/>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L878" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54128,7 +55980,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K880" t="inlineStr"/>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L880" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54189,7 +56045,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K881" t="inlineStr"/>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L881" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54250,7 +56110,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K882" t="inlineStr"/>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L882" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54372,7 +56236,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K884" t="inlineStr"/>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L884" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54494,7 +56362,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K886" t="inlineStr"/>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L886" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54677,7 +56549,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K889" t="inlineStr"/>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L889" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54738,7 +56614,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K890" t="inlineStr"/>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L890" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54921,7 +56801,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K893" t="inlineStr"/>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L893" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55043,7 +56927,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K895" t="inlineStr"/>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L895" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55104,7 +56992,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K896" t="inlineStr"/>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L896" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55165,7 +57057,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K897" t="inlineStr"/>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L897" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55348,7 +57244,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K900" t="inlineStr"/>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L900" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55409,7 +57309,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L901" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55531,7 +57435,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K903" t="inlineStr"/>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L903" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55714,7 +57622,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K906" t="inlineStr"/>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L906" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55958,7 +57870,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L910" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56019,7 +57935,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K911" t="inlineStr"/>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L911" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56080,7 +58000,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K912" t="inlineStr"/>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L912" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56202,7 +58126,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L914" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56324,7 +58252,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K916" t="inlineStr"/>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L916" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56751,7 +58683,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K923" t="inlineStr"/>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L923" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56812,7 +58748,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K924" t="inlineStr"/>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L924" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56873,7 +58813,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr"/>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L925" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57056,7 +59000,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr"/>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L928" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57361,7 +59309,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K933" t="inlineStr"/>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L933" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57422,7 +59374,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K934" t="inlineStr"/>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L934" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57483,7 +59439,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L935" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57605,7 +59565,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K937" t="inlineStr"/>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L937" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57666,7 +59630,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K938" t="inlineStr"/>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L938" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57971,7 +59939,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L943" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58032,7 +60004,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K944" t="inlineStr"/>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L944" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58093,7 +60069,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K945" t="inlineStr"/>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L945" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58215,7 +60195,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K947" t="inlineStr"/>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L947" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58276,7 +60260,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K948" t="inlineStr"/>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L948" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58337,7 +60325,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K949" t="inlineStr"/>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L949" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58398,7 +60390,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K950" t="inlineStr"/>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L950" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58520,7 +60516,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K952" t="inlineStr"/>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L952" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58642,7 +60642,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K954" t="inlineStr"/>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L954" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58825,7 +60829,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K957" t="inlineStr"/>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L957" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58886,7 +60894,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K958" t="inlineStr"/>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L958" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58947,7 +60959,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K959" t="inlineStr"/>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L959" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59134,7 +61150,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K962" t="inlineStr"/>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L962" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59195,7 +61215,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K963" t="inlineStr"/>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L963" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59439,7 +61463,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K967" t="inlineStr"/>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L967" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59500,7 +61528,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K968" t="inlineStr"/>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L968" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59561,7 +61593,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K969" t="inlineStr"/>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L969" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59744,7 +61780,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K972" t="inlineStr"/>
+      <c r="K972" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L972" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59866,7 +61906,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K974" t="inlineStr"/>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L974" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59927,7 +61971,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K975" t="inlineStr"/>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L975" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60049,7 +62097,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K977" t="inlineStr"/>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L977" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60171,7 +62223,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K979" t="inlineStr"/>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L979" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60232,7 +62288,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K980" t="inlineStr"/>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L980" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60415,7 +62475,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K983" t="inlineStr"/>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L983" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60476,7 +62540,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K984" t="inlineStr"/>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L984" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60537,7 +62605,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K985" t="inlineStr"/>
+      <c r="K985" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L985" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60598,7 +62670,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K986" t="inlineStr"/>
+      <c r="K986" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L986" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60659,7 +62735,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K987" t="inlineStr"/>
+      <c r="K987" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L987" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60720,7 +62800,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K988" t="inlineStr"/>
+      <c r="K988" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L988" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60903,7 +62987,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K991" t="inlineStr"/>
+      <c r="K991" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L991" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60964,7 +63052,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K992" t="inlineStr"/>
+      <c r="K992" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L992" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61025,7 +63117,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K993" t="inlineStr"/>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L993" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61086,7 +63182,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K994" t="inlineStr"/>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L994" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61147,7 +63247,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K995" t="inlineStr"/>
+      <c r="K995" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L995" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61269,7 +63373,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K997" t="inlineStr"/>
+      <c r="K997" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L997" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61330,7 +63438,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K998" t="inlineStr"/>
+      <c r="K998" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L998" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61574,7 +63686,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1002" t="inlineStr"/>
+      <c r="K1002" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1002" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61696,7 +63812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1004" t="inlineStr"/>
+      <c r="K1004" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1004" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61879,7 +63999,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1007" t="inlineStr"/>
+      <c r="K1007" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1007" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61940,7 +64064,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1008" t="inlineStr"/>
+      <c r="K1008" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1008" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62001,7 +64129,11 @@
           <t>77.145.084-9</t>
         </is>
       </c>
-      <c r="K1009" t="inlineStr"/>
+      <c r="K1009" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L1009" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62062,7 +64194,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K1010" t="inlineStr"/>
+      <c r="K1010" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1010" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62123,7 +64259,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K1011" t="inlineStr"/>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1011" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62184,7 +64324,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1012" t="inlineStr"/>
+      <c r="K1012" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1012" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62306,7 +64450,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K1014" t="inlineStr"/>
+      <c r="K1014" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1014" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62428,7 +64576,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1016" t="inlineStr"/>
+      <c r="K1016" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1016" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62672,7 +64824,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1020" t="inlineStr"/>
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1020" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62916,7 +65072,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K1024" t="inlineStr"/>
+      <c r="K1024" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1024" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63038,7 +65198,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K1026" t="inlineStr"/>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1026" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63099,7 +65263,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K1027" t="inlineStr"/>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1027" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63160,7 +65328,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1028" t="inlineStr"/>
+      <c r="K1028" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1028" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63221,7 +65393,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K1029" t="inlineStr"/>
+      <c r="K1029" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1029" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63343,7 +65519,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K1031" t="inlineStr"/>
+      <c r="K1031" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1031" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63404,7 +65584,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K1032" t="inlineStr"/>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1032" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63465,7 +65649,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K1033" t="inlineStr"/>
+      <c r="K1033" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1033" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63526,7 +65714,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1034" t="inlineStr"/>
+      <c r="K1034" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1034" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63587,7 +65779,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1035" t="inlineStr"/>
+      <c r="K1035" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1035" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63770,7 +65966,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K1038" t="inlineStr"/>
+      <c r="K1038" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1038" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64075,7 +66275,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1043" t="inlineStr"/>
+      <c r="K1043" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1043" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64197,7 +66401,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K1045" t="inlineStr"/>
+      <c r="K1045" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1045" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64258,7 +66466,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1046" t="inlineStr"/>
+      <c r="K1046" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1046" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64441,7 +66653,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1049" t="inlineStr"/>
+      <c r="K1049" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1049" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64502,7 +66718,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1050" t="inlineStr"/>
+      <c r="K1050" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1050" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64563,7 +66783,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1051" t="inlineStr"/>
+      <c r="K1051" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1051" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64685,7 +66909,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K1053" t="inlineStr"/>
+      <c r="K1053" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1053" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64990,7 +67218,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1058" t="inlineStr"/>
+      <c r="K1058" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1058" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65051,7 +67283,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1059" t="inlineStr"/>
+      <c r="K1059" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1059" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65112,7 +67348,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1060" t="inlineStr"/>
+      <c r="K1060" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1060" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65295,7 +67535,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K1063" t="inlineStr"/>
+      <c r="K1063" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1063" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65417,7 +67661,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1065" t="inlineStr"/>
+      <c r="K1065" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1065" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65478,7 +67726,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1066" t="inlineStr"/>
+      <c r="K1066" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1066" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65539,7 +67791,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1067" t="inlineStr"/>
+      <c r="K1067" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1067" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65600,7 +67856,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1068" t="inlineStr"/>
+      <c r="K1068" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1068" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65661,7 +67921,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1069" t="inlineStr"/>
+      <c r="K1069" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1069" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65722,7 +67986,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K1070" t="inlineStr"/>
+      <c r="K1070" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1070" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65966,7 +68234,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1074" t="inlineStr"/>
+      <c r="K1074" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1074" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66210,7 +68482,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1078" t="inlineStr"/>
+      <c r="K1078" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1078" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66271,7 +68547,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1079" t="inlineStr"/>
+      <c r="K1079" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1079" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66454,7 +68734,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K1082" t="inlineStr"/>
+      <c r="K1082" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1082" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66515,7 +68799,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1083" t="inlineStr"/>
+      <c r="K1083" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1083" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66637,7 +68925,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K1085" t="inlineStr"/>
+      <c r="K1085" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1085" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66881,7 +69173,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1089" t="inlineStr"/>
+      <c r="K1089" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1089" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67064,7 +69360,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K1092" t="inlineStr"/>
+      <c r="K1092" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1092" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67125,7 +69425,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1093" t="inlineStr"/>
+      <c r="K1093" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1093" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67247,7 +69551,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1095" t="inlineStr"/>
+      <c r="K1095" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1095" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/los-lagos.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/los-lagos.xlsx
@@ -1452,7 +1452,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2781,7 +2785,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3976,7 +3984,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4037,7 +4049,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5167,7 +5183,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5480,7 +5500,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6057,7 +6081,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6825,7 +6853,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8967,7 +8999,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10166,7 +10202,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11743,7 +11783,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17653,7 +17697,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18649,7 +18697,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21218,7 +21270,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +24591,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37788,7 +37848,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40568,7 +40632,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40694,7 +40762,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42031,7 +42103,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44262,7 +44338,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45095,7 +45175,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46335,7 +46419,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47095,7 +47183,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48034,7 +48126,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48095,7 +48191,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48790,7 +48890,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51505,7 +51609,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K809" t="inlineStr"/>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L809" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51627,7 +51735,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K811" t="inlineStr"/>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L811" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53021,7 +53133,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K833" t="inlineStr"/>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L833" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55667,7 +55783,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K875" t="inlineStr"/>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L875" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56175,7 +56295,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L883" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56679,7 +56803,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K891" t="inlineStr"/>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L891" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58500,7 +58628,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K920" t="inlineStr"/>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L920" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59126,7 +59258,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K930" t="inlineStr"/>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L930" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60134,7 +60270,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K946" t="inlineStr"/>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L946" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61845,7 +61985,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K973" t="inlineStr"/>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L973" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62036,7 +62180,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K976" t="inlineStr"/>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L976" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63312,7 +63460,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K996" t="inlineStr"/>
+      <c r="K996" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L996" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63751,7 +63903,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1003" t="inlineStr"/>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1003" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68299,7 +68455,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1075" t="inlineStr"/>
+      <c r="K1075" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1075" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68421,7 +68581,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1077" t="inlineStr"/>
+      <c r="K1077" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1077" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69490,7 +69654,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1094" t="inlineStr"/>
+      <c r="K1094" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1094" t="inlineStr">
         <is>
           <t>USD</t>
